--- a/data/daily/2026-09/2026-09-01.xlsx
+++ b/data/daily/2026-09/2026-09-01.xlsx
@@ -1170,14 +1170,114 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,210 +1292,110 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,232 +1425,232 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[사은품 증정/센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
+          <t>[센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821174846_45143a0db27240d2a750fe3ec9963935.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260901110153_bb9a8b1870e2492e99dbbf1747444c66.jpg</t>
         </is>
       </c>
     </row>
@@ -2844,27 +2844,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
+          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>옵티젠</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>59,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/11090567</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260703113258_219f277f4a66466ea414f5539beed475.jpg</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2949,34 +2949,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
+          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>46,900원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2984,27 +2984,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>46,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>옵티젠</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[사은품 증정/센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
+          <t>[센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
+          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>59,900원</t>
         </is>
       </c>
     </row>
@@ -3698,12 +3698,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
+          <t>아일로</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>아일로</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
+          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
+          <t>65,900원</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
           <t>46,900원</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>65,900원</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4062,34 +4062,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>오브맘 면역＆프로폴리스 하루구미 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602129&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/XgyvZV5zt5ig9XLyfDOS613602129_00_01XgyvZV5zt5ig9XLyfDOS.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4147,19 +4147,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627034&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260810/jotmVom4KndGXbIlPcuj032627034_00_01jotmVom4KndGXbIlPcuj.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>오브맘 더채움 비오틴 하루구미 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/mhxyGp5yOjC4MHfaY2J8613602127_00_01mhxyGp5yOjC4MHfaY2J8.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
     </row>
@@ -4202,12 +4202,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
+          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4217,19 +4217,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=025575127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/VsX5iaJon2xHHTs8AQHv025575127_00_01VsX5iaJon2xHHTs8AQHv.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260409/2cHZmOZUJJcZL1ip2bls610910968_00_002cHZmOZUJJcZL1ip2bls.png</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 철분 30정 30일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4247,17 +4247,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
     </row>
@@ -4272,27 +4272,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>오브맘 눈건강 루테인 하루구미 30일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251015/CucIwXdPFflEtkJEtXZl613602126_00_01CucIwXdPFflEtkJEtXZl.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
         </is>
       </c>
     </row>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4317,24 +4317,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>유한양행 비피더스 생유산균 10캡슐 10일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4357,19 +4357,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651650&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/wjBYMQTwSs5Uxawy8JxO600651650_00_00wjBYMQTwSs5Uxawy8JxO.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4377,27 +4377,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 루테인 30정 30일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
     </row>
@@ -4512,52 +4512,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
         </is>
       </c>
     </row>
@@ -4569,27 +4569,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
     </row>
@@ -4626,52 +4626,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 면역＆프로폴리스 하루구미 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 더채움 비오틴 하루구미 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
+          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 철분 30정 30일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 눈건강 루테인 하루구미 30일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>유한양행 비피더스 생유산균 10캡슐 10일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 루테인 30정 30일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
     </row>
@@ -4683,52 +4683,52 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4910,34 +4910,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>빌드 프리미엄 테프 효소 유산균 30포 (1개월분)</t>
+          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19,950원</t>
+          <t>14,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000235606&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023560605ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355476ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4945,27 +4945,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24,460원</t>
+          <t>31,300원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733450ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -4980,27 +4980,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+          <t>[올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17,960원</t>
+          <t>8,990원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000186228&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018622875ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5015,34 +5015,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11,900원</t>
+          <t>34,010원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549618ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5050,34 +5050,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[9월 올영픽/산리오콜라보] [반값특가] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31,300원</t>
+          <t>11,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014343ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5085,34 +5085,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>락토핏</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>11,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199062&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019906245ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5120,34 +5120,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>34,010원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549618ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5155,27 +5155,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>덴프스 트루바이타민 액티브 10+4포 증정기획 (2주분)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>12,900원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000263560&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026356006ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5190,27 +5190,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14,900원</t>
+          <t>24,460원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355476ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733450ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -5330,19 +5330,19 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
@@ -5350,22 +5350,22 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5387,47 +5387,47 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>칼로(Kalo)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>판도라</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>빌드</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>락토핏</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
         </is>
       </c>
     </row>
@@ -5444,47 +5444,47 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>빌드 프리미엄 테프 효소 유산균 30포 (1개월분)</t>
+          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/산리오콜라보] [반값특가] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 트루바이타민 액티브 10+4포 증정기획 (2주분)</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
     </row>
@@ -5501,47 +5501,47 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>19,950원</t>
+          <t>14,900원</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
+          <t>31,300원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>8,990원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>34,010원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>11,900원</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>11,900원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
           <t>24,460원</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>17,960원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>11,900원</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>31,300원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>17,900원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>34,010원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>12,900원</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>14,900원</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
@@ -5683,7 +5683,7 @@
         <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -5702,10 +5702,10 @@
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -5733,29 +5733,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5768,16 +5768,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5787,10 +5787,10 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -5799,7 +5799,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5821,7 +5821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5831,13 +5831,79 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
